--- a/ClientExcel/Game/EntityGroup.xlsx
+++ b/ClientExcel/Game/EntityGroup.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="21">
   <si>
     <t>#</t>
   </si>
@@ -66,6 +66,9 @@
   </si>
   <si>
     <t>策划备注</t>
+  </si>
+  <si>
+    <t>实体组编号枚举名</t>
   </si>
   <si>
     <t>组名称</t>
@@ -1039,13 +1042,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H9"/>
-  <sheetFormatPr defaultColWidth="23.5" defaultRowHeight="13.5" outlineLevelCol="7"/>
+  <dimension ref="A1:I9"/>
+  <sheetFormatPr defaultColWidth="23.5" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="16384" width="23.5" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25" spans="1:6">
+    <row r="1" ht="14.25" spans="1:7">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1056,8 +1059,9 @@
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
     </row>
-    <row r="2" ht="14.25" spans="1:8">
+    <row r="2" ht="14.25" spans="1:9">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -1065,23 +1069,24 @@
         <v>2</v>
       </c>
       <c r="C2" s="2"/>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="2"/>
+      <c r="E2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" ht="14.25" spans="1:8">
+    <row r="3" ht="14.25" spans="1:9">
       <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
@@ -1089,23 +1094,24 @@
         <v>8</v>
       </c>
       <c r="C3" s="2"/>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="2"/>
+      <c r="E3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="F3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="G3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" ht="14.25" spans="1:8">
+    <row r="4" ht="14.25" spans="1:9">
       <c r="A4" s="2" t="s">
         <v>0</v>
       </c>
@@ -1124,68 +1130,78 @@
       <c r="F4" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="G4" s="2" t="s">
         <v>16</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>17</v>
       </c>
+      <c r="I4" s="1" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="5" ht="14.25" spans="1:8">
+    <row r="5" ht="14.25" spans="1:9">
       <c r="A5" s="2"/>
       <c r="B5" s="2">
         <v>1</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E5" s="2">
+        <v>20</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F5" s="2">
         <v>60</v>
       </c>
-      <c r="F5" s="2">
+      <c r="G5" s="2">
         <v>1</v>
       </c>
-      <c r="G5" s="1">
+      <c r="H5" s="1">
         <v>60</v>
       </c>
-      <c r="H5" s="1">
+      <c r="I5" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="6" ht="14.25" spans="1:6">
+    <row r="6" ht="14.25" spans="1:7">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
       <c r="D6" s="3"/>
-      <c r="E6" s="2"/>
+      <c r="E6" s="3"/>
       <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
     </row>
-    <row r="7" ht="14.25" spans="1:6">
+    <row r="7" ht="14.25" spans="1:7">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
       <c r="D7" s="3"/>
-      <c r="E7" s="2"/>
+      <c r="E7" s="3"/>
       <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
     </row>
-    <row r="8" ht="14.25" spans="1:6">
+    <row r="8" ht="14.25" spans="1:7">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
       <c r="D8" s="3"/>
-      <c r="E8" s="2"/>
+      <c r="E8" s="3"/>
       <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
     </row>
-    <row r="9" ht="14.25" spans="1:6">
+    <row r="9" ht="14.25" spans="1:7">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
       <c r="D9" s="3"/>
-      <c r="E9" s="2"/>
+      <c r="E9" s="3"/>
       <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
